--- a/output/pdf_financials_xlsx/BST.xlsx
+++ b/output/pdf_financials_xlsx/BST.xlsx
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>4.14971</v>
+        <v>8.327036</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.465691</v>
+        <v>4.963593</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.568129</v>
+        <v>1.148977</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.6868069999999999</v>
+        <v>1.414811</v>
       </c>
       <c r="K91" s="3" t="n">
         <v>0</v>
@@ -5415,40 +5415,40 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.991181</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.991181</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.991181</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.004482</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.054056</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.054056</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.056536</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.056536</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.056536</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.056536</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.056536</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.056536</v>
       </c>
     </row>
     <row r="93">
@@ -8572,7 +8572,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10220,7 +10224,11 @@
           <t>RESERVE (Note 10)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -15974,7 +15982,11 @@
           <t>RESERVE (Note 9)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16910,7 +16922,11 @@
           <t>RESERVE (Note 6)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BST.xlsx
+++ b/output/pdf_financials_xlsx/BST.xlsx
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005116</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00105</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         <v>0.003765</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002548</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.007933000000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005581</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000161</v>
       </c>
     </row>
     <row r="13">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.280538</v>
+        <v>-0.285654</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.630667</v>
+        <v>-0.631717</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2042,16 +2042,16 @@
         <v>-0.119209</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.152649</v>
+        <v>-0.155197</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.093389</v>
+        <v>-0.101322</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.87722</v>
+        <v>-0.8828009999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.155517</v>
+        <v>-0.155678</v>
       </c>
     </row>
     <row r="28">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.280538</v>
+        <v>-0.285654</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.630667</v>
+        <v>-0.631717</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2164,16 +2164,16 @@
         <v>-0.119209</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.152649</v>
+        <v>-0.155197</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.093389</v>
+        <v>-0.101322</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.87722</v>
+        <v>-0.8828009999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.155517</v>
+        <v>-0.155678</v>
       </c>
     </row>
     <row r="30">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E321" s="5" t="n">
@@ -35124,7 +35124,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E325" s="5" t="n">

--- a/output/pdf_financials_xlsx/BST.xlsx
+++ b/output/pdf_financials_xlsx/BST.xlsx
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -21056,7 +21056,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -22200,7 +22204,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -23190,7 +23198,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -26266,7 +26278,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -27224,7 +27240,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
